--- a/data/trans_dic/IQ2605_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ2605_R2-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51,99%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73,49%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>83,95%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>49,59%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>72,36%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>79,38%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,96; 58,74</t>
+          <t>43,76; 60,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,65; 79,08</t>
+          <t>64,85; 80,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,33; 87,16</t>
+          <t>72,01; 88,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,77; 96,37</t>
+          <t>59,49; 95,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,47; 60,2</t>
+          <t>41,39; 58,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,04; 80,76</t>
+          <t>64,26; 79,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,9; 88,47</t>
+          <t>69,54; 86,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,73; 92,8</t>
+          <t>43,36; 91,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,78; 56,87</t>
+          <t>44,16; 56,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67,03; 77,91</t>
+          <t>67,33; 78,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,9; 86,6</t>
+          <t>74,55; 86,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,56; 91,08</t>
+          <t>64,15; 90,42</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>54,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>73,27%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,28; 58,45</t>
+          <t>47,52; 54,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,64; 76,46</t>
+          <t>70,5; 77,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,9; 78,22</t>
+          <t>74,97; 80,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,32; 77,89</t>
+          <t>69,29; 82,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,48; 55,15</t>
+          <t>50,17; 58,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,64; 77,43</t>
+          <t>69,79; 76,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,07; 81,05</t>
+          <t>71,93; 78,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,77; 83,08</t>
+          <t>60,63; 77,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,04; 55,36</t>
+          <t>49,83; 55,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,09; 75,9</t>
+          <t>70,87; 75,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,49; 79,26</t>
+          <t>74,31; 79,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,46; 79,27</t>
+          <t>68,15; 78,19</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>58,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>73,7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>55,61%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>75,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>76,32%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>58,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,24; 61,66</t>
+          <t>52,05; 64,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,08; 80,69</t>
+          <t>65,12; 77,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,21; 81,51</t>
+          <t>75,81; 84,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62,63; 84,06</t>
+          <t>58,98; 84,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 65,47</t>
+          <t>49,76; 62,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,92; 76,5</t>
+          <t>69,29; 80,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,92; 85,62</t>
+          <t>69,96; 81,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,65; 85,22</t>
+          <t>62,44; 84,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,63; 61,76</t>
+          <t>52,74; 61,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,77; 76,76</t>
+          <t>68,41; 76,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74,87; 82,01</t>
+          <t>74,33; 82,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,57; 81,63</t>
+          <t>65,27; 81,58</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73,21%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,7; 56,96</t>
+          <t>49,51; 55,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,62</t>
+          <t>70,45; 75,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,37; 78,56</t>
+          <t>76,43; 81,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65,58; 77,76</t>
+          <t>70,69; 81,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,73; 55,52</t>
+          <t>51,06; 57,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,47; 75,91</t>
+          <t>70,61; 76,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,32; 81,49</t>
+          <t>73,26; 78,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,27; 82,03</t>
+          <t>64,42; 77,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,98; 55,45</t>
+          <t>51,03; 55,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,47; 75,33</t>
+          <t>71,36; 75,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75,76; 79,45</t>
+          <t>75,71; 79,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,5; 78,57</t>
+          <t>69,65; 78,26</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43809</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56409</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>44097</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>65210</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>46681</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8782</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43809</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62380</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56409</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>16362</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37317; 52238</t>
+          <t>36875; 51071</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57364; 71271</t>
+          <t>55048; 68473</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41358; 51259</t>
+          <t>49408; 60791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5939; 10848</t>
+          <t>7373; 11831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36630; 50729</t>
+          <t>36802; 51666</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54362; 68555</t>
+          <t>57910; 71581</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50018; 60702</t>
+          <t>40894; 51054</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7707; 12833</t>
+          <t>3600; 7574</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77558; 98487</t>
+          <t>76488; 98131</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117305; 136342</t>
+          <t>117833; 136578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94160; 110350</t>
+          <t>94996; 109822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15945; 22849</t>
+          <t>13275; 18711</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>467</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>238745</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>351404</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>380157</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94009</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>220328</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>321169</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>350911</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>238745</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>351404</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>380157</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>60621</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>164277</t>
+          <t>154630</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204333; 237537</t>
+          <t>222443; 255726</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>305266; 335147</t>
+          <t>335432; 367144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>334275; 363637</t>
+          <t>364740; 393743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54325; 68998</t>
+          <t>85145; 101827</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>222260; 258140</t>
+          <t>203906; 237910</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>336105; 368424</t>
+          <t>305916; 335916</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>365213; 394309</t>
+          <t>334410; 365440</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92945; 110673</t>
+          <t>53102; 67808</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>437612; 484118</t>
+          <t>435732; 483506</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>649845; 693815</t>
+          <t>647831; 693217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>708673; 754078</t>
+          <t>707017; 753811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>151854; 175831</t>
+          <t>143433; 164557</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>193</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,39 +1852,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>116334</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147208</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31754</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>94154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>119926</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>128499</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32437</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90121</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>116334</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>147208</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>32818</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65256</t>
+          <t>64571</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83372; 104400</t>
+          <t>79916; 99606</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110130; 128644</t>
+          <t>106431; 126431</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118210; 137230</t>
+          <t>138151; 154782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27088; 36353</t>
+          <t>25410; 36442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80405; 100517</t>
+          <t>84252; 105064</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>106097; 125021</t>
+          <t>110461; 128535</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>138343; 156012</t>
+          <t>117788; 136723</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27569; 38112</t>
+          <t>27256; 36870</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>169920; 199391</t>
+          <t>170284; 198300</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222025; 247814</t>
+          <t>220882; 247790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>262503; 287509</t>
+          <t>260596; 288145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57680; 71809</t>
+          <t>56618; 70759</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>372675</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>530118</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>372675</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>530118</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>336981; 378576</t>
+          <t>349455; 392941</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>486435; 527029</t>
+          <t>510185; 550137</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>507772; 543676</t>
+          <t>563535; 600903</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93844; 111272</t>
+          <t>126085; 145254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>351075; 391885</t>
+          <t>339361; 379085</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>510291; 549655</t>
+          <t>485730; 525483</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>562734; 600860</t>
+          <t>507027; 543833</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>134765; 157301</t>
+          <t>89886; 107975</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>698754; 760010</t>
+          <t>699407; 757448</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1009213; 1063594</t>
+          <t>1007544; 1063101</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1082965; 1135614</t>
+          <t>1082220; 1134290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>236071; 263118</t>
+          <t>221415; 248795</t>
         </is>
       </c>
     </row>
